--- a/Lab Work/Lab 3 Amit Bikram Mishra.xlsx
+++ b/Lab Work/Lab 3 Amit Bikram Mishra.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMIT\Desktop\ANUDIP\AmitAnudipAF057117047\Lab Work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC15741-1E65-4F83-94A5-A58211E21D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6C55EF-F66C-4C88-BEDC-6185BC29DF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,60 +328,60 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="8">
     <dxf>
       <font>
         <strike/>
@@ -390,6 +390,19 @@
     <dxf>
       <font>
         <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF65EC40"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
       </font>
     </dxf>
     <dxf>
@@ -406,46 +419,8 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -454,152 +429,6 @@
         <strike val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF65EC40"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1044,69 +873,69 @@
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="29"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="30"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="29"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="31"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1116,36 +945,36 @@
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B16:I16"/>
   </mergeCells>
-  <conditionalFormatting sqref="D2:D9">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="greaterThanOrEqual">
-      <formula>150</formula>
-    </cfRule>
-    <cfRule type="top10" dxfId="13" priority="5" rank="3"/>
-    <cfRule type="expression" dxfId="12" priority="4">
-      <formula>AND($A2="Product B",$B2="North")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:D9">
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$A2="Product A"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B16:I16">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="5. Apply conditional formatting to highlight sales for &quot;Product B&quot; in the &quot;North&quot; region.">
+      <formula>NOT(ISERROR(SEARCH("5. Apply conditional formatting to highlight sales for ""Product B"" in the ""North"" region.",B16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C9">
-    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="2024-01">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="2024-01">
       <formula>NOT(ISERROR(SEARCH("2024-01",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>AND($A2="Product B",$B2="North")</formula>
+    </cfRule>
+    <cfRule type="top10" dxfId="3" priority="5" rank="3"/>
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThanOrEqual">
+      <formula>150</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>"g"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"ghf"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:I16">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="5. Apply conditional formatting to highlight sales for &quot;Product B&quot; in the &quot;North&quot; region.">
-      <formula>NOT(ISERROR(SEARCH("5. Apply conditional formatting to highlight sales for ""Product B"" in the ""North"" region.",B16)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"g"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
